--- a/testcase/textcase_ngan.xlsx
+++ b/testcase/textcase_ngan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6790"/>
+    <workbookView windowWidth="18750" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="391">
   <si>
     <t>Test case ID</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Expected result</t>
   </si>
   <si>
+    <t>Lỗi xảy ra</t>
+  </si>
+  <si>
     <t>Note</t>
   </si>
   <si>
@@ -72,6 +75,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>-</t>
     </r>
     <r>
@@ -94,6 +103,9 @@
     </r>
   </si>
   <si>
+    <t>Danh sách lịch khám trong ngày hiện tại không hiển thị đầy đủ dù hệ thống có dữ liệu lịch hẹn hợp lệ trong ngày.</t>
+  </si>
+  <si>
     <t>PASS</t>
   </si>
   <si>
@@ -110,6 +122,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">- </t>
     </r>
     <r>
@@ -138,7 +156,36 @@
     <t>Ngày rỗng (VD: 01/01/2023)</t>
   </si>
   <si>
-    <t>Hiển thị thông báo “Không có lịch khám”</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hiển thị thông báo “Không có lịch khám”</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi không có lịch khám trong ngày, hệ thống không hiển thị thông báo “Không có dữ liệu” mà chỉ hiển thị màn hình trống.</t>
   </si>
   <si>
     <t>TC_03</t>
@@ -159,6 +206,9 @@
     <t>Hiển thị thông báo lỗi, không crash UI</t>
   </si>
   <si>
+    <t>Khi API trả lỗi, hệ thống không hiển thị thông báo lỗi phù hợp và không xử lý fallback dữ liệu.</t>
+  </si>
+  <si>
     <t>TC_04</t>
   </si>
   <si>
@@ -175,6 +225,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Hiển thị danh sách đầy đủ</t>
     </r>
     <r>
@@ -198,6 +254,32 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Danh sách lịch khám tải rất chậm hoặc bị treo khi số lượng lịch khám lớn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Không lag</t>
     </r>
     <r>
@@ -230,6 +312,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Nhấn</t>
     </r>
     <r>
@@ -258,6 +346,9 @@
     <t>Hiển thị chi tiết:</t>
   </si>
   <si>
+    <t>Khi xem chi tiết một lịch khám, một số thông tin như bác sĩ hoặc khoa không hiển thị đầy đủ.</t>
+  </si>
+  <si>
     <t>- Bệnh nhân</t>
   </si>
   <si>
@@ -265,6 +356,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Thời gian</t>
     </r>
     <r>
@@ -299,6 +396,9 @@
     <t>Hiển thị thông báo “Lịch không tồn tại”</t>
   </si>
   <si>
+    <t>Hệ thống vẫn cho phép truy cập chi tiết lịch khám đã bị xoá thay vì hiển thị thông báo lỗi.</t>
+  </si>
+  <si>
     <t>TC_07</t>
   </si>
   <si>
@@ -323,6 +423,26 @@
     <t>- Cập nhật thành công</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Sau khi cập nhật trạng thái lịch khám, trạng thái mới không được cập nhật ngay trên danh sách</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <t>- Hiển thị thông báo thành công</t>
   </si>
   <si>
@@ -344,6 +464,9 @@
     <t>Hiển thị lỗi “Không thể cập nhật trạng thái”</t>
   </si>
   <si>
+    <t>Hệ thống vẫn cho phép lưu trạng thái không hợp lệ mà không hiển thị cảnh báo</t>
+  </si>
+  <si>
     <t>TC_09</t>
   </si>
   <si>
@@ -362,6 +485,9 @@
     <t>Hiển thị thông báo lỗi, trạng thái không đổi</t>
   </si>
   <si>
+    <t>Khi mất kết nối mạng trong lúc cập nhật trạng thái, hệ thống không hiển thị thông báo lỗi và không rollback dữ liệu.</t>
+  </si>
+  <si>
     <t>TC_10</t>
   </si>
   <si>
@@ -371,9 +497,57 @@
     <t>Có bệnh nhân “Nguyễn Văn A”</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
+    <t>1. Nhập “Nguyễn Văn A” vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>2. Nhấn tìm kiếm</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng lịch của BN</t>
+  </si>
+  <si>
+    <t>Tìm kiếm lịch theo tên bệnh nhân trả về kết quả không chính xác hoặc thiếu dữ liệu.</t>
+  </si>
+  <si>
+    <t>TC_11</t>
+  </si>
+  <si>
+    <t>Tìm kiếm không có kết quả</t>
+  </si>
+  <si>
+    <t>Không có BN tên “ABCXYZ”</t>
+  </si>
+  <si>
+    <t>1. Nhập “ABCXYZ” vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>ABCXYZ</t>
+  </si>
+  <si>
+    <t>Hiển thị “Không tìm thấy lịch”</t>
+  </si>
+  <si>
+    <t>Khi tìm kiếm không có kết quả, hệ thống không hiển thị thông báo phù hợp cho người dùng.</t>
+  </si>
+  <si>
+    <t>TC_12</t>
+  </si>
+  <si>
+    <t>Tìm kiếm với ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Đang ở màn hình tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Nhập ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>@@@###</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -381,86 +555,6 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>Nhập “Nguyễn Văn A” vào ô tìm kiếm</t>
-    </r>
-  </si>
-  <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <r>
-      <t>2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhấn tìm kiếm</t>
-    </r>
-  </si>
-  <si>
-    <t>Hiển thị đúng lịch của BN</t>
-  </si>
-  <si>
-    <t>TC_11</t>
-  </si>
-  <si>
-    <t>Tìm kiếm không có kết quả</t>
-  </si>
-  <si>
-    <t>Không có BN tên “ABCXYZ”</t>
-  </si>
-  <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập “ABCXYZ” vào ô tìm kiếm</t>
-    </r>
-  </si>
-  <si>
-    <t>ABCXYZ</t>
-  </si>
-  <si>
-    <t>Hiển thị “Không tìm thấy lịch”</t>
-  </si>
-  <si>
-    <t>TC_12</t>
-  </si>
-  <si>
-    <t>Tìm kiếm với ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t>Đang ở màn hình tìm kiếm</t>
-  </si>
-  <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập ký tự đặc biệt</t>
-    </r>
-  </si>
-  <si>
-    <t>@@@###</t>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Thông </t>
     </r>
     <r>
@@ -483,15 +577,72 @@
     </r>
   </si>
   <si>
+    <t>Tìm kiếm với ký tự đặc biệt làm hệ thống hiển thị lỗi hoặc không trả kết quả.</t>
+  </si>
+  <si>
     <t>TC_13</t>
   </si>
   <si>
     <t>Tìm kiếm với chuỗi rất dài</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
+    <t>1. Nhập chuỗi dài</t>
+  </si>
+  <si>
+    <t>256+ ký tự</t>
+  </si>
+  <si>
+    <t>Khi nhập chuỗi tìm kiếm quá dài, hệ thống phản hồi chậm hoặc không xử lý đúng.</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>Xem thống kê lịch theo ngày</t>
+  </si>
+  <si>
+    <t>Có lịch trong ngày</t>
+  </si>
+  <si>
+    <t>1. Chọn ngày</t>
+  </si>
+  <si>
+    <t>2. Xem thống kê</t>
+  </si>
+  <si>
+    <t>Hiển thị tổng số lịch đúng</t>
+  </si>
+  <si>
+    <t>Thống kê lịch theo ngày hiển thị sai số lượng so với dữ liệu thực tế.</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t>Thống kê khi API trả lỗi</t>
+  </si>
+  <si>
+    <t>API thống kê lỗi</t>
+  </si>
+  <si>
+    <t>API 500</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi</t>
+  </si>
+  <si>
+    <t>Khi API thống kê trả lỗi, hệ thống không hiển thị thông báo lỗi rõ ràng.</t>
+  </si>
+  <si>
+    <t>TC_16</t>
+  </si>
+  <si>
+    <t>Xem hồ sơ bệnh nhân</t>
+  </si>
+  <si>
+    <t>Bệnh Nhân đã tồn tại</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -499,56 +650,6 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>Nhập chuỗi dài</t>
-    </r>
-  </si>
-  <si>
-    <t>256+ ký tự</t>
-  </si>
-  <si>
-    <t>TC_14</t>
-  </si>
-  <si>
-    <t>Xem thống kê lịch theo ngày</t>
-  </si>
-  <si>
-    <t>Có lịch trong ngày</t>
-  </si>
-  <si>
-    <t>1. Chọn ngày</t>
-  </si>
-  <si>
-    <t>2. Xem thống kê</t>
-  </si>
-  <si>
-    <t>Hiển thị tổng số lịch đúng</t>
-  </si>
-  <si>
-    <t>TC_15</t>
-  </si>
-  <si>
-    <t>Thống kê khi API trả lỗi</t>
-  </si>
-  <si>
-    <t>API thống kê lỗi</t>
-  </si>
-  <si>
-    <t>API 500</t>
-  </si>
-  <si>
-    <t>Hiển thị thông báo lỗi</t>
-  </si>
-  <si>
-    <t>TC_16</t>
-  </si>
-  <si>
-    <t>Xem hồ sơ bệnh nhân</t>
-  </si>
-  <si>
-    <t>Bệnh Nhân đã tồn tại</t>
-  </si>
-  <si>
-    <r>
       <t>Nhấn</t>
     </r>
     <r>
@@ -577,6 +678,9 @@
     <t>Hiển thị đúng thông tin cá nhân</t>
   </si>
   <si>
+    <t>Hồ sơ bệnh nhân hiển thị thiếu thông tin cá nhân.</t>
+  </si>
+  <si>
     <t>TC_17</t>
   </si>
   <si>
@@ -592,6 +696,9 @@
     <t>Hiển thị danh sách các lần khám</t>
   </si>
   <si>
+    <t>Lịch sử khám hiển thị không đầy đủ các lần khám trước đó.</t>
+  </si>
+  <si>
     <t>TC_18</t>
   </si>
   <si>
@@ -610,6 +717,9 @@
     <t>Hiển thị “Chưa có lịch sử khám”</t>
   </si>
   <si>
+    <t>Hệ thống không hiển thị thông báo khi bệnh nhân không có lịch sử khám.</t>
+  </si>
+  <si>
     <t>TC_19</t>
   </si>
   <si>
@@ -631,6 +741,9 @@
     <t>Ghi chú được lưu thành công</t>
   </si>
   <si>
+    <t>Thêm ghi chú điều trị nhưng dữ liệu không được lưu thành công.</t>
+  </si>
+  <si>
     <t>TC_20</t>
   </si>
   <si>
@@ -646,6 +759,9 @@
     <t>Hiển thị lỗi validate</t>
   </si>
   <si>
+    <t>Hệ thống vẫn cho phép thêm ghi chú rỗng.</t>
+  </si>
+  <si>
     <t>TC_21</t>
   </si>
   <si>
@@ -658,6 +774,9 @@
     <t>Hiển thị đã xóa thành công</t>
   </si>
   <si>
+    <t>Sau khi xoá ghi chú, dữ liệu vẫn hiển thị cho đến khi tải lại trang.</t>
+  </si>
+  <si>
     <t>TC_22</t>
   </si>
   <si>
@@ -670,6 +789,9 @@
     <t>Hiển thị lỗi hoặc giới hạn ký tự</t>
   </si>
   <si>
+    <t>Thêm ghi chú quá dài làm vỡ giao diện hoặc không có cảnh báo giới hạn ký tự.</t>
+  </si>
+  <si>
     <t>TC_23</t>
   </si>
   <si>
@@ -682,6 +804,9 @@
     <t>Thông báo lỗi, không lưu</t>
   </si>
   <si>
+    <t>Khi mất mạng trong lúc lưu ghi chú, hệ thống không hiển thị thông báo lỗi.</t>
+  </si>
+  <si>
     <t>TC_24</t>
   </si>
   <si>
@@ -703,6 +828,9 @@
     <t>Lịch được cập nhật ngày giờ mới</t>
   </si>
   <si>
+    <t>Đổi lịch khám nhưng thông tin lịch mới không được cập nhật đồng bộ.</t>
+  </si>
+  <si>
     <t>TC_25</t>
   </si>
   <si>
@@ -727,6 +855,9 @@
     <t>Hồ sơ bị xóa khỏi hệ thống</t>
   </si>
   <si>
+    <t>Hệ thống cho phép xoá hồ sơ bệnh án mà không yêu cầu xác nhận.</t>
+  </si>
+  <si>
     <t>TC_26</t>
   </si>
   <si>
@@ -754,12 +885,22 @@
     <t>Ngày: 20/12/2025 – 09:00</t>
   </si>
   <si>
-    <t>- Đặt lịch thành công,
-- Hiển thị lịch mới trong danh sách gồm:
-+ Tên BN
-+ Khoa
-+ Bác sĩ
-+ Ngày</t>
+    <t>- Đặt lịch thành công,</t>
+  </si>
+  <si>
+    <t>Đặt lịch hẹn mới nhưng dữ liệu không được lưu đầy đủ.</t>
+  </si>
+  <si>
+    <t>- Hiển thị lịch mới trong danh sách gồm:</t>
+  </si>
+  <si>
+    <t>+ Khoa</t>
+  </si>
+  <si>
+    <t>+ Bác sĩ</t>
+  </si>
+  <si>
+    <t>+ Ngày</t>
   </si>
   <si>
     <t>TC_27</t>
@@ -777,6 +918,9 @@
     <t>Hiển thị thông báo lỗi "vui lòng đặt tên bệnh nhân "</t>
   </si>
   <si>
+    <t>Hệ thống không hiển thị thông báo lỗi khi không nhập tên bệnh nhân.</t>
+  </si>
+  <si>
     <t>TC_28</t>
   </si>
   <si>
@@ -792,6 +936,9 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn khoa"</t>
   </si>
   <si>
+    <t>Không nhập khoa nhưng hệ thống vẫn cho phép đặt lịch hẹn.</t>
+  </si>
+  <si>
     <t>TC_29</t>
   </si>
   <si>
@@ -807,6 +954,9 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn bác sĩ"</t>
   </si>
   <si>
+    <t>Không nhập bác sĩ nhưng lịch hẹn vẫn được tạo.</t>
+  </si>
+  <si>
     <t>TC_30</t>
   </si>
   <si>
@@ -822,6 +972,9 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn ngày hẹn"</t>
   </si>
   <si>
+    <t>Không nhập ngày khám nhưng hệ thống không cảnh báo lỗi.</t>
+  </si>
+  <si>
     <t>TC_31</t>
   </si>
   <si>
@@ -834,6 +987,9 @@
     <t>Hiển thị thông báo lỗi "Vui lòng nhập thông tin lịch hẹn"</t>
   </si>
   <si>
+    <t>Không nhập bất kỳ thông tin nào nhưng vẫn có thể gửi form đặt lịch.</t>
+  </si>
+  <si>
     <t>TC_32</t>
   </si>
   <si>
@@ -852,6 +1008,9 @@
     <t>Hiển thị đầy đủ, không lag</t>
   </si>
   <si>
+    <t>Lịch sử lịch hẹn hiển thị thiếu hoặc sai dữ liệu.</t>
+  </si>
+  <si>
     <t>TC_33</t>
   </si>
   <si>
@@ -870,6 +1029,9 @@
     <t>Chỉ hiển thị lịch trong ngày đã chọn</t>
   </si>
   <si>
+    <t>Lọc lịch hẹn theo ngày trả về kết quả không chính xác.</t>
+  </si>
+  <si>
     <t>TC_34</t>
   </si>
   <si>
@@ -888,6 +1050,9 @@
     <t>Hiển thị lịch trong tuần được chọn</t>
   </si>
   <si>
+    <t>Lọc lịch hẹn theo tuần hiển thị sai phạm vi ngày.</t>
+  </si>
+  <si>
     <t>TC_35</t>
   </si>
   <si>
@@ -906,6 +1071,9 @@
     <t>Hiển thị lịch trong tháng 12</t>
   </si>
   <si>
+    <t>Lọc lịch hẹn theo tháng không bao gồm đầy đủ các lịch trong tháng.</t>
+  </si>
+  <si>
     <t>TC_36</t>
   </si>
   <si>
@@ -930,6 +1098,9 @@
     <t>Trạng thái lịch chuyển sang “Đã hủy”</t>
   </si>
   <si>
+    <t>Sau khi huỷ lịch hẹn thành công, trạng thái không được cập nhật ngay.</t>
+  </si>
+  <si>
     <t>TC_37</t>
   </si>
   <si>
@@ -951,6 +1122,9 @@
     <t>Tạo lịch hẹn thành công</t>
   </si>
   <si>
+    <t>Thêm lịch hẹn thành công nhưng không hiển thị trên danh sách.</t>
+  </si>
+  <si>
     <t>TC_38</t>
   </si>
   <si>
@@ -966,6 +1140,9 @@
     <t>Hiển thị lỗi "Thêm không hợp lệ"</t>
   </si>
   <si>
+    <t>Không nhập khoa nhưng hệ thống chỉ báo lỗi chung chung, không rõ ràng.</t>
+  </si>
+  <si>
     <t>TC_39</t>
   </si>
   <si>
@@ -978,6 +1155,9 @@
     <t>Hiển thị lỗi "Ngày không hợp lệ"</t>
   </si>
   <si>
+    <t>Không nhập ngày nhưng thông báo lỗi không đúng vị trí.</t>
+  </si>
+  <si>
     <t>TC_40</t>
   </si>
   <si>
@@ -987,18 +1167,7 @@
     <t>có nhiều lịch thuộc các khoa khác nhau</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập tên khoa vào ô tìm kiếm</t>
-    </r>
+    <t>1. Nhập tên khoa vào ô tìm kiếm</t>
   </si>
   <si>
     <t>khoa Nhi</t>
@@ -1007,6 +1176,9 @@
     <t>Hiển thị lịch thuộc khoa Nhi</t>
   </si>
   <si>
+    <t>Tìm kiếm lịch hẹn theo khoa trả về dữ liệu không liên quan.</t>
+  </si>
+  <si>
     <t>TC_41</t>
   </si>
   <si>
@@ -1016,18 +1188,7 @@
     <t>có lịch gán cho bác sĩ</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập tên bác sĩ</t>
-    </r>
+    <t>1. Nhập tên bác sĩ</t>
   </si>
   <si>
     <t>BS Trần B</t>
@@ -1036,6 +1197,9 @@
     <t>Hiển thị lịch của bác sĩ Trần B</t>
   </si>
   <si>
+    <t>Tìm kiếm theo bác sĩ không phân biệt chính xác bác sĩ trùng tên.</t>
+  </si>
+  <si>
     <t>TC_42</t>
   </si>
   <si>
@@ -1054,6 +1218,9 @@
     <t>Trạng thái chuyển sang “Đã tiếp nhận"</t>
   </si>
   <si>
+    <t>Hệ thống cho phép tiếp nhận bệnh nhân trước thời gian lịch hẹn.</t>
+  </si>
+  <si>
     <t>TC_43</t>
   </si>
   <si>
@@ -1069,6 +1236,9 @@
     <t>Hiển thị lỗi, không cho tiếp nhận</t>
   </si>
   <si>
+    <t>Vẫn cho phép tiếp nhận bệnh nhân với lịch hẹn đã bị huỷ.</t>
+  </si>
+  <si>
     <t>TC_44</t>
   </si>
   <si>
@@ -1078,18 +1248,7 @@
     <t>Lịch tồn tại</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập mã lịch</t>
-    </r>
+    <t>1. Nhập mã lịch</t>
   </si>
   <si>
     <t>LH004</t>
@@ -1098,6 +1257,9 @@
     <t>Hiển thị đúng lịch hẹn</t>
   </si>
   <si>
+    <t>Tìm kiếm theo mã lịch hẹn không trả về kết quả dù mã tồn tại.</t>
+  </si>
+  <si>
     <t>TC_45</t>
   </si>
   <si>
@@ -1107,23 +1269,15 @@
     <t>Bệnh nhân có số điện thoại</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập số điện thoại</t>
-    </r>
+    <t>1. Nhập số điện thoại</t>
   </si>
   <si>
     <t>Hiển thị lịch của bệnh nhân</t>
   </si>
   <si>
+    <t>Tìm kiếm theo số điện thoại trả về sai bệnh nhân.</t>
+  </si>
+  <si>
     <t>TC_46</t>
   </si>
   <si>
@@ -1133,23 +1287,15 @@
     <t>CCCD đã lưu trong hệ thống</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập CCCD</t>
-    </r>
+    <t>1. Nhập CCCD</t>
   </si>
   <si>
     <t>Hiển thị đúng bệnh nhân</t>
   </si>
   <si>
+    <t>Tìm kiếm theo CCCD không hoạt động đúng.</t>
+  </si>
+  <si>
     <t>TC_47</t>
   </si>
   <si>
@@ -1159,18 +1305,7 @@
     <t>Có bệnh nhân trong ngày cần kiếm</t>
   </si>
   <si>
-    <r>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Nhập tên, mã lịch hẹn, sđt</t>
-    </r>
+    <t>1. Nhập tên, mã lịch hẹn, sđt</t>
   </si>
   <si>
     <t>Mã BN: BN006</t>
@@ -1182,6 +1317,9 @@
     <t>Hiển thị bệnh nhân trong ngày</t>
   </si>
   <si>
+    <t>Danh sách bệnh nhân trong ngày hiển thị thiếu dữ liệu.</t>
+  </si>
+  <si>
     <t>TC_48</t>
   </si>
   <si>
@@ -1197,6 +1335,9 @@
     <t>Hiển thị danh sách bệnh nhân đúng ngày</t>
   </si>
   <si>
+    <t>Xem danh sách bệnh nhân theo ngày nhưng dữ liệu không đồng bộ.</t>
+  </si>
+  <si>
     <t>TC_49</t>
   </si>
   <si>
@@ -1215,6 +1356,9 @@
     <t>Hiển thi đúng dữ liệu trang 2</t>
   </si>
   <si>
+    <t>Phân trang danh sách bệnh nhân không hoạt động đúng.</t>
+  </si>
+  <si>
     <t>TC_50</t>
   </si>
   <si>
@@ -1230,6 +1374,9 @@
     <t>Hệ thống chuyển về màn hình đăng nhập</t>
   </si>
   <si>
+    <t>Người dùng chưa đăng nhập vẫn truy cập được màn hình hẹn.</t>
+  </si>
+  <si>
     <t>TC_51</t>
   </si>
   <si>
@@ -1245,6 +1392,9 @@
     <t>2. Chọn ngày quá khứ</t>
   </si>
   <si>
+    <t>Hệ thống cho phép đặt lịch hẹn với ngày trong quá khứ.</t>
+  </si>
+  <si>
     <t>TC_52</t>
   </si>
   <si>
@@ -1260,6 +1410,12 @@
     <t>Hiển thị lỗi "Bác sĩ đã có lịch"</t>
   </si>
   <si>
+    <t>Hệ thống không kiểm tra trùng giờ khám của bác sĩ.</t>
+  </si>
+  <si>
+    <t>12/20/2025 9:00</t>
+  </si>
+  <si>
     <t>TC_53</t>
   </si>
   <si>
@@ -1278,6 +1434,9 @@
     <t>Hiển thị trang trống hoặc tự quay về trang cuối</t>
   </si>
   <si>
+    <t>Truy cập trang vượt quá số trang nhưng không có thông báo lỗi.</t>
+  </si>
+  <si>
     <t>TC_54</t>
   </si>
   <si>
@@ -1288,20 +1447,22 @@
   </si>
   <si>
     <t>Truy cập màn hình lịch</t>
+  </si>
+  <si>
+    <t>Khi API tải lịch trả lỗi, hệ thống không xử lý và không hiển thị thông báo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="m/d/yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1464,6 +1625,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1666,7 +1833,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1684,6 +1851,69 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1813,7 +2043,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1825,34 +2055,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1937,7 +2167,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1947,23 +2177,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2498,18 +2746,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G142"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H150"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818" customWidth="1"/>
     <col min="2" max="2" width="24.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="21.4545454545455" customWidth="1"/>
     <col min="4" max="4" width="23.1818181818182" customWidth="1"/>
     <col min="5" max="5" width="22.5454545454545" customWidth="1"/>
-    <col min="6" max="6" width="39.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="32.9090909090909" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2531,517 +2780,557 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
       <c r="G2" s="3"/>
-    </row>
-    <row r="3" ht="70" spans="1:7">
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="3"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="2"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="2"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
       <c r="D8" s="2"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
       <c r="D9" s="2"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:7">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" ht="84" spans="1:7">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" ht="28" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="G12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="H12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:8">
+      <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
-      <c r="A14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="G14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:8">
+      <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
-      <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="G15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:8">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="G16" s="5"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="1"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7">
+        <v>50</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="F20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="G20" s="10"/>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="10"/>
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" ht="28" spans="1:7">
-      <c r="A22" s="1" t="s">
+      <c r="G22" s="11"/>
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" ht="56" spans="1:7">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="1:7">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="G23" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" ht="56" spans="1:7">
+      <c r="F24" s="2"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" ht="28" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="D25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="3"/>
-    </row>
-    <row r="26" ht="28" spans="1:7">
-      <c r="A26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" ht="56" spans="1:7">
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" ht="28" spans="1:7">
+      <c r="D27" s="2"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="D28" s="2"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" ht="28" spans="1:7">
+      <c r="F28" s="2"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="3"/>
-    </row>
-    <row r="30" ht="28" spans="1:7">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" ht="28" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="3"/>
-    </row>
-    <row r="31" ht="28" spans="1:7">
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:7">
+        <v>78</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="D33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="D35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:7">
-      <c r="A36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:8">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3049,1775 +3338,2094 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>93</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" s="13">
+        <v>45916</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:8">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" ht="28" spans="1:7">
-      <c r="A43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="5">
-        <v>45916</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" ht="28" spans="1:7">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" ht="28" spans="1:7">
-      <c r="A45" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="3"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="D59" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="3"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="3"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="3"/>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" ht="42" customHeight="1" spans="1:7">
+        <v>174</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>163</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="3"/>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="3"/>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="2"/>
+      <c r="C63" s="1"/>
       <c r="D63" s="2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>182</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E64" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="3"/>
-    </row>
-    <row r="65" ht="42" customHeight="1" spans="1:7">
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" ht="42" customHeight="1" spans="1:8">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="C65" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="3"/>
-    </row>
-    <row r="66" ht="28" spans="1:7">
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="3"/>
-    </row>
-    <row r="67" ht="42" spans="1:7">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="2"/>
       <c r="F67" s="1"/>
       <c r="G67" s="3"/>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
-      <c r="D68" s="2"/>
+      <c r="D68" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="E68" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="3"/>
-    </row>
-    <row r="69" ht="84" spans="1:7">
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E70" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="F70" s="1"/>
       <c r="G70" s="3"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:7">
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:8">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
-      <c r="D71" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="D71" s="2"/>
       <c r="E71" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="3"/>
-    </row>
-    <row r="72" ht="28" spans="1:7">
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:8">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F72" s="1"/>
-      <c r="G72" s="3"/>
-    </row>
-    <row r="73" ht="42" spans="1:7">
+      <c r="D72" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F73" s="1"/>
-      <c r="G73" s="3"/>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="E73" s="2"/>
+      <c r="F73" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="3"/>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>170</v>
-      </c>
+      <c r="F75" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="3"/>
-    </row>
-    <row r="77" ht="42" customHeight="1" spans="1:7">
+      <c r="F76" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G76" s="5"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" ht="42" customHeight="1" spans="1:8">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E78" s="2"/>
       <c r="F78" s="1"/>
       <c r="G78" s="3"/>
-    </row>
-    <row r="79" ht="42" spans="1:7">
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:8">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
-      <c r="D79" s="2"/>
+      <c r="D79" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="E79" s="2" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="3"/>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="3"/>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E82" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="F82" s="1"/>
       <c r="G82" s="3"/>
-    </row>
-    <row r="83" ht="42" customHeight="1" spans="1:7">
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" ht="42" customHeight="1" spans="1:8">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="3"/>
-    </row>
-    <row r="84" ht="28" spans="1:7">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E84" s="2"/>
       <c r="F84" s="1"/>
       <c r="G84" s="3"/>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:8">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="2"/>
+      <c r="D85" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="E85" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="3"/>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="3"/>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
-      <c r="D87" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E88" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F87" s="1"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="F88" s="1"/>
       <c r="G88" s="3"/>
-    </row>
-    <row r="89" ht="42" customHeight="1" spans="1:7">
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" ht="42" customHeight="1" spans="1:8">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F89" s="1"/>
-      <c r="G89" s="3"/>
-    </row>
-    <row r="90" ht="28" spans="1:7">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E90" s="2"/>
       <c r="F90" s="1"/>
       <c r="G90" s="3"/>
-    </row>
-    <row r="91" ht="42" spans="1:7">
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:8">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
-      <c r="D91" s="2"/>
+      <c r="D91" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="E91" s="2" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="3"/>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="3"/>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" ht="27.5" customHeight="1" spans="1:7">
-      <c r="A94" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E94" s="3"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" ht="27.5" customHeight="1" spans="1:8">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="F94" s="1"/>
       <c r="G94" s="3"/>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="3"/>
-    </row>
-    <row r="96" ht="28" customHeight="1" spans="1:7">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
+      <c r="D95" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="D96" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E96" s="3"/>
+        <v>196</v>
+      </c>
+      <c r="E96" s="2"/>
       <c r="F96" s="1"/>
       <c r="G96" s="3"/>
-    </row>
-    <row r="97" ht="26" customHeight="1" spans="1:7">
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" ht="26" customHeight="1" spans="1:8">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E97" s="3"/>
-      <c r="F97" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" ht="29" customHeight="1" spans="1:8">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F98" s="1"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" ht="27" customHeight="1" spans="1:8">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" ht="29" customHeight="1" spans="1:7">
-      <c r="A98" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G98" s="3"/>
-    </row>
-    <row r="99" ht="27" customHeight="1" spans="1:7">
-      <c r="A99" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E99" s="5">
-        <v>46012</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="3"/>
-    </row>
-    <row r="100" ht="29" customHeight="1" spans="1:7">
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" ht="29" customHeight="1" spans="1:8">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
-      <c r="D100" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" ht="27" customHeight="1" spans="1:7">
-      <c r="A101" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F100" s="1"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" ht="27" customHeight="1" spans="1:8">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2"/>
       <c r="F101" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" ht="36" customHeight="1" spans="1:7">
+        <v>230</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" ht="31" customHeight="1" spans="1:7">
-      <c r="A103" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E103" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" ht="31" customHeight="1" spans="1:8">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="3"/>
       <c r="F103" s="1"/>
       <c r="G103" s="3"/>
-    </row>
-    <row r="104" ht="26" customHeight="1" spans="1:7">
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" ht="26" customHeight="1" spans="1:8">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>230</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="E104" s="3"/>
       <c r="F104" s="1"/>
       <c r="G104" s="3"/>
-    </row>
-    <row r="105" ht="26" customHeight="1" spans="1:7">
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" ht="26" customHeight="1" spans="1:8">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E105" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E105" s="3"/>
       <c r="F105" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1" spans="1:7">
+        <v>235</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="3"/>
-    </row>
-    <row r="107" ht="29" customHeight="1" spans="1:7">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
+        <v>239</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" ht="29" customHeight="1" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>246</v>
+      </c>
       <c r="D107" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
+      </c>
+      <c r="E107" s="13">
+        <v>46012</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="3"/>
-    </row>
-    <row r="108" ht="26" customHeight="1" spans="1:7">
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" ht="26" customHeight="1" spans="1:8">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="2" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" ht="29" customHeight="1" spans="1:7">
+        <v>249</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" ht="29" customHeight="1" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="3"/>
-    </row>
-    <row r="110" ht="25" customHeight="1" spans="1:7">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="2" t="s">
-        <v>242</v>
+        <v>253</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" ht="25" customHeight="1" spans="1:8">
+      <c r="A110" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F110" s="1"/>
-      <c r="G110" s="3"/>
-    </row>
-    <row r="111" ht="27" customHeight="1" spans="1:7">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
+        <v>262</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" ht="27" customHeight="1" spans="1:8">
+      <c r="A111" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="D111" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" ht="26" customHeight="1" spans="1:7">
-      <c r="A112" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>235</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" ht="26" customHeight="1" spans="1:8">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
       <c r="D112" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E112" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="F112" s="1"/>
       <c r="G112" s="3"/>
-    </row>
-    <row r="113" ht="33" customHeight="1" spans="1:7">
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" ht="33" customHeight="1" spans="1:8">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F113" s="1"/>
-      <c r="G113" s="3"/>
-    </row>
-    <row r="114" ht="26" customHeight="1" spans="1:7">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1" spans="1:8">
+      <c r="A114" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="D114" s="2" t="s">
-        <v>62</v>
+        <v>277</v>
       </c>
       <c r="E114" s="1"/>
-      <c r="F114" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" ht="30" customHeight="1" spans="1:7">
-      <c r="A115" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>252</v>
+      <c r="F114" s="1"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" ht="30" customHeight="1" spans="1:8">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="3"/>
-    </row>
-    <row r="116" ht="25" customHeight="1" spans="1:7">
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" ht="25" customHeight="1" spans="1:8">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
-      <c r="D116" s="1" t="s">
-        <v>82</v>
+      <c r="D116" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" ht="29" customHeight="1" spans="1:7">
+        <v>280</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" ht="29" customHeight="1" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>259</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="3"/>
-    </row>
-    <row r="118" ht="35" customHeight="1" spans="1:7">
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" ht="35" customHeight="1" spans="1:8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
-      <c r="D118" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" ht="29" customHeight="1" spans="1:7">
-      <c r="A119" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>263</v>
-      </c>
+      <c r="D118" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F118" s="1"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" ht="29" customHeight="1" spans="1:8">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
       <c r="D119" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F119" s="1"/>
-      <c r="G119" s="3"/>
-    </row>
-    <row r="120" ht="29" customHeight="1" spans="1:7">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" ht="29" customHeight="1" spans="1:8">
+      <c r="A120" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="D120" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E120" s="1"/>
-      <c r="F120" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" ht="25" customHeight="1" spans="1:7">
-      <c r="A121" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>269</v>
-      </c>
+      <c r="F120" s="1"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" ht="25" customHeight="1" spans="1:8">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
       <c r="D121" s="2" t="s">
-        <v>228</v>
+        <v>284</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="3"/>
-    </row>
-    <row r="122" ht="30" customHeight="1" spans="1:7">
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" ht="30" customHeight="1" spans="1:8">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="2" t="s">
-        <v>265</v>
+        <v>69</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="123" ht="26" customHeight="1" spans="1:7">
+        <v>291</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="3"/>
-    </row>
-    <row r="124" ht="31" customHeight="1" spans="1:7">
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" ht="31" customHeight="1" spans="1:8">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="125" ht="32" customHeight="1" spans="1:7">
+        <v>298</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" ht="32" customHeight="1" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E125" s="1">
-        <v>912345678</v>
+        <v>303</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="3"/>
-    </row>
-    <row r="126" ht="28" customHeight="1" spans="1:7">
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" ht="28" customHeight="1" spans="1:8">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="127" ht="37" customHeight="1" spans="1:7">
+        <v>305</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" ht="37" customHeight="1" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E127" s="1">
-        <v>79123456789</v>
+        <v>309</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="3"/>
-    </row>
-    <row r="128" ht="41" customHeight="1" spans="1:7">
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" ht="41" customHeight="1" spans="1:8">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
-      <c r="D128" s="1" t="s">
-        <v>82</v>
+      <c r="D128" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G128" s="3"/>
-    </row>
-    <row r="129" ht="42" customHeight="1" spans="1:7">
+        <v>312</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>172</v>
+        <v>316</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="3"/>
-    </row>
-    <row r="130" ht="28" spans="1:7">
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F130" s="1"/>
-      <c r="G130" s="3"/>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="2" t="s">
-        <v>293</v>
+      <c r="D130" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="3"/>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E132" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="E132" s="1"/>
       <c r="F132" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="133" ht="31" customHeight="1" spans="1:7">
+        <v>325</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" ht="31" customHeight="1" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E133" s="5">
-        <v>46015</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134" ht="27" customHeight="1" spans="1:7">
-      <c r="A134" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>302</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E133" s="1">
+        <v>912345678</v>
+      </c>
+      <c r="F133" s="1"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" ht="27" customHeight="1" spans="1:8">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
       <c r="D134" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>304</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="135" ht="29" customHeight="1" spans="1:7">
+        <v>331</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" ht="29" customHeight="1" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E135" s="3"/>
-      <c r="F135" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" ht="26" customHeight="1" spans="1:7">
-      <c r="A136" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>314</v>
+        <v>336</v>
+      </c>
+      <c r="E135" s="1">
+        <v>79123456789</v>
+      </c>
+      <c r="F135" s="1"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" ht="26" customHeight="1" spans="1:8">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="3"/>
-    </row>
-    <row r="137" ht="24" customHeight="1" spans="1:7">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E137" s="5">
-        <v>42109</v>
+      <c r="F136" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="H136" s="3"/>
+    </row>
+    <row r="137" ht="24" customHeight="1" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="3"/>
-    </row>
-    <row r="138" ht="24" customHeight="1" spans="1:7">
+      <c r="H137" s="3"/>
+    </row>
+    <row r="138" ht="24" customHeight="1" spans="1:8">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
-      <c r="D138" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="139" ht="28" customHeight="1" spans="1:7">
-      <c r="A139" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>319</v>
-      </c>
+      <c r="D138" s="1"/>
+      <c r="E138" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F138" s="1"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" ht="28" customHeight="1" spans="1:8">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
       <c r="E139" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="140" ht="25" customHeight="1" spans="1:7">
+        <v>344</v>
+      </c>
+      <c r="F139" s="1"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" ht="25" customHeight="1" spans="1:8">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="6">
-        <v>46011.375</v>
-      </c>
-      <c r="F140" s="1"/>
-      <c r="G140" s="3"/>
-    </row>
-    <row r="141" ht="26" customHeight="1" spans="1:7">
+      <c r="D140" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" ht="26" customHeight="1" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>325</v>
+        <v>349</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E141" s="13">
+        <v>46015</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" ht="25" customHeight="1" spans="1:7">
+        <v>351</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" ht="25" customHeight="1" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>15</v>
+        <v>358</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E143" s="3"/>
+      <c r="F143" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E145" s="13">
+        <v>42109</v>
+      </c>
+      <c r="F145" s="1"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:8">
+      <c r="A147" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="1"/>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="122">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A89:A92"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A129:A131"/>
-    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A147:A148"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B20"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B77:B80"/>
-    <mergeCell ref="B83:B86"/>
-    <mergeCell ref="B89:B92"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="B79:B82"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B147:B148"/>
     <mergeCell ref="C4:C9"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C83:C86"/>
-    <mergeCell ref="C89:C92"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="C129:C131"/>
-    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="C72:C77"/>
+    <mergeCell ref="C79:C82"/>
+    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="C91:C94"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C137:C139"/>
+    <mergeCell ref="C147:C148"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D20"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="D77:D80"/>
-    <mergeCell ref="D83:D86"/>
-    <mergeCell ref="D89:D92"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="D129:D131"/>
-    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D18:D22"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="D72:D77"/>
+    <mergeCell ref="D79:D82"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="D91:D94"/>
+    <mergeCell ref="D97:D100"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="D137:D139"/>
+    <mergeCell ref="D147:D148"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E16:E20"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E72:E77"/>
+    <mergeCell ref="E102:E103"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F83:F86"/>
-    <mergeCell ref="F89:F92"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="F129:F131"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G83:G86"/>
-    <mergeCell ref="G89:G92"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G129:G131"/>
-    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="F68:F71"/>
+    <mergeCell ref="F79:F82"/>
+    <mergeCell ref="F85:F88"/>
+    <mergeCell ref="F91:F94"/>
+    <mergeCell ref="F97:F100"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="F137:F139"/>
+    <mergeCell ref="F147:F148"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G72:G77"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="H18:H22"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="H68:H71"/>
+    <mergeCell ref="H72:H77"/>
+    <mergeCell ref="H79:H82"/>
+    <mergeCell ref="H85:H88"/>
+    <mergeCell ref="H91:H94"/>
+    <mergeCell ref="H97:H100"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="H137:H139"/>
+    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/testcase/textcase_ngan.xlsx
+++ b/testcase/textcase_ngan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18750" windowHeight="6800"/>
+    <workbookView windowWidth="18750" windowHeight="7520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="336">
   <si>
     <t>Test case ID</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Expected result</t>
-  </si>
-  <si>
-    <t>Lỗi xảy ra</t>
   </si>
   <si>
     <t>Note</t>
@@ -103,9 +100,6 @@
     </r>
   </si>
   <si>
-    <t>Danh sách lịch khám trong ngày hiện tại không hiển thị đầy đủ dù hệ thống có dữ liệu lịch hẹn hợp lệ trong ngày.</t>
-  </si>
-  <si>
     <t>PASS</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     </r>
   </si>
   <si>
-    <t>Khi không có lịch khám trong ngày, hệ thống không hiển thị thông báo “Không có dữ liệu” mà chỉ hiển thị màn hình trống.</t>
-  </si>
-  <si>
     <t>TC_03</t>
   </si>
   <si>
@@ -204,9 +195,6 @@
   </si>
   <si>
     <t>Hiển thị thông báo lỗi, không crash UI</t>
-  </si>
-  <si>
-    <t>Khi API trả lỗi, hệ thống không hiển thị thông báo lỗi phù hợp và không xử lý fallback dữ liệu.</t>
   </si>
   <si>
     <t>TC_04</t>
@@ -256,26 +244,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Danh sách lịch khám tải rất chậm hoặc bị treo khi số lượng lịch khám lớn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -346,9 +314,6 @@
     <t>Hiển thị chi tiết:</t>
   </si>
   <si>
-    <t>Khi xem chi tiết một lịch khám, một số thông tin như bác sĩ hoặc khoa không hiển thị đầy đủ.</t>
-  </si>
-  <si>
     <t>- Bệnh nhân</t>
   </si>
   <si>
@@ -396,9 +361,6 @@
     <t>Hiển thị thông báo “Lịch không tồn tại”</t>
   </si>
   <si>
-    <t>Hệ thống vẫn cho phép truy cập chi tiết lịch khám đã bị xoá thay vì hiển thị thông báo lỗi.</t>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
@@ -423,26 +385,6 @@
     <t>- Cập nhật thành công</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Sau khi cập nhật trạng thái lịch khám, trạng thái mới không được cập nhật ngay trên danh sách</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>- Hiển thị thông báo thành công</t>
   </si>
   <si>
@@ -464,9 +406,6 @@
     <t>Hiển thị lỗi “Không thể cập nhật trạng thái”</t>
   </si>
   <si>
-    <t>Hệ thống vẫn cho phép lưu trạng thái không hợp lệ mà không hiển thị cảnh báo</t>
-  </si>
-  <si>
     <t>TC_09</t>
   </si>
   <si>
@@ -485,9 +424,6 @@
     <t>Hiển thị thông báo lỗi, trạng thái không đổi</t>
   </si>
   <si>
-    <t>Khi mất kết nối mạng trong lúc cập nhật trạng thái, hệ thống không hiển thị thông báo lỗi và không rollback dữ liệu.</t>
-  </si>
-  <si>
     <t>TC_10</t>
   </si>
   <si>
@@ -509,9 +445,6 @@
     <t>Hiển thị đúng lịch của BN</t>
   </si>
   <si>
-    <t>Tìm kiếm lịch theo tên bệnh nhân trả về kết quả không chính xác hoặc thiếu dữ liệu.</t>
-  </si>
-  <si>
     <t>TC_11</t>
   </si>
   <si>
@@ -528,9 +461,6 @@
   </si>
   <si>
     <t>Hiển thị “Không tìm thấy lịch”</t>
-  </si>
-  <si>
-    <t>Khi tìm kiếm không có kết quả, hệ thống không hiển thị thông báo phù hợp cho người dùng.</t>
   </si>
   <si>
     <t>TC_12</t>
@@ -577,9 +507,6 @@
     </r>
   </si>
   <si>
-    <t>Tìm kiếm với ký tự đặc biệt làm hệ thống hiển thị lỗi hoặc không trả kết quả.</t>
-  </si>
-  <si>
     <t>TC_13</t>
   </si>
   <si>
@@ -592,9 +519,6 @@
     <t>256+ ký tự</t>
   </si>
   <si>
-    <t>Khi nhập chuỗi tìm kiếm quá dài, hệ thống phản hồi chậm hoặc không xử lý đúng.</t>
-  </si>
-  <si>
     <t>TC_14</t>
   </si>
   <si>
@@ -613,9 +537,6 @@
     <t>Hiển thị tổng số lịch đúng</t>
   </si>
   <si>
-    <t>Thống kê lịch theo ngày hiển thị sai số lượng so với dữ liệu thực tế.</t>
-  </si>
-  <si>
     <t>TC_15</t>
   </si>
   <si>
@@ -629,9 +550,6 @@
   </si>
   <si>
     <t>Hiển thị thông báo lỗi</t>
-  </si>
-  <si>
-    <t>Khi API thống kê trả lỗi, hệ thống không hiển thị thông báo lỗi rõ ràng.</t>
   </si>
   <si>
     <t>TC_16</t>
@@ -678,9 +596,6 @@
     <t>Hiển thị đúng thông tin cá nhân</t>
   </si>
   <si>
-    <t>Hồ sơ bệnh nhân hiển thị thiếu thông tin cá nhân.</t>
-  </si>
-  <si>
     <t>TC_17</t>
   </si>
   <si>
@@ -696,9 +611,6 @@
     <t>Hiển thị danh sách các lần khám</t>
   </si>
   <si>
-    <t>Lịch sử khám hiển thị không đầy đủ các lần khám trước đó.</t>
-  </si>
-  <si>
     <t>TC_18</t>
   </si>
   <si>
@@ -717,9 +629,6 @@
     <t>Hiển thị “Chưa có lịch sử khám”</t>
   </si>
   <si>
-    <t>Hệ thống không hiển thị thông báo khi bệnh nhân không có lịch sử khám.</t>
-  </si>
-  <si>
     <t>TC_19</t>
   </si>
   <si>
@@ -741,9 +650,6 @@
     <t>Ghi chú được lưu thành công</t>
   </si>
   <si>
-    <t>Thêm ghi chú điều trị nhưng dữ liệu không được lưu thành công.</t>
-  </si>
-  <si>
     <t>TC_20</t>
   </si>
   <si>
@@ -759,9 +665,6 @@
     <t>Hiển thị lỗi validate</t>
   </si>
   <si>
-    <t>Hệ thống vẫn cho phép thêm ghi chú rỗng.</t>
-  </si>
-  <si>
     <t>TC_21</t>
   </si>
   <si>
@@ -774,9 +677,6 @@
     <t>Hiển thị đã xóa thành công</t>
   </si>
   <si>
-    <t>Sau khi xoá ghi chú, dữ liệu vẫn hiển thị cho đến khi tải lại trang.</t>
-  </si>
-  <si>
     <t>TC_22</t>
   </si>
   <si>
@@ -789,9 +689,6 @@
     <t>Hiển thị lỗi hoặc giới hạn ký tự</t>
   </si>
   <si>
-    <t>Thêm ghi chú quá dài làm vỡ giao diện hoặc không có cảnh báo giới hạn ký tự.</t>
-  </si>
-  <si>
     <t>TC_23</t>
   </si>
   <si>
@@ -804,9 +701,6 @@
     <t>Thông báo lỗi, không lưu</t>
   </si>
   <si>
-    <t>Khi mất mạng trong lúc lưu ghi chú, hệ thống không hiển thị thông báo lỗi.</t>
-  </si>
-  <si>
     <t>TC_24</t>
   </si>
   <si>
@@ -828,9 +722,6 @@
     <t>Lịch được cập nhật ngày giờ mới</t>
   </si>
   <si>
-    <t>Đổi lịch khám nhưng thông tin lịch mới không được cập nhật đồng bộ.</t>
-  </si>
-  <si>
     <t>TC_25</t>
   </si>
   <si>
@@ -855,9 +746,6 @@
     <t>Hồ sơ bị xóa khỏi hệ thống</t>
   </si>
   <si>
-    <t>Hệ thống cho phép xoá hồ sơ bệnh án mà không yêu cầu xác nhận.</t>
-  </si>
-  <si>
     <t>TC_26</t>
   </si>
   <si>
@@ -888,9 +776,6 @@
     <t>- Đặt lịch thành công,</t>
   </si>
   <si>
-    <t>Đặt lịch hẹn mới nhưng dữ liệu không được lưu đầy đủ.</t>
-  </si>
-  <si>
     <t>- Hiển thị lịch mới trong danh sách gồm:</t>
   </si>
   <si>
@@ -918,9 +803,6 @@
     <t>Hiển thị thông báo lỗi "vui lòng đặt tên bệnh nhân "</t>
   </si>
   <si>
-    <t>Hệ thống không hiển thị thông báo lỗi khi không nhập tên bệnh nhân.</t>
-  </si>
-  <si>
     <t>TC_28</t>
   </si>
   <si>
@@ -936,9 +818,6 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn khoa"</t>
   </si>
   <si>
-    <t>Không nhập khoa nhưng hệ thống vẫn cho phép đặt lịch hẹn.</t>
-  </si>
-  <si>
     <t>TC_29</t>
   </si>
   <si>
@@ -954,9 +833,6 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn bác sĩ"</t>
   </si>
   <si>
-    <t>Không nhập bác sĩ nhưng lịch hẹn vẫn được tạo.</t>
-  </si>
-  <si>
     <t>TC_30</t>
   </si>
   <si>
@@ -972,9 +848,6 @@
     <t>Hiển thị thông báo lỗi "Vui lòng chọn ngày hẹn"</t>
   </si>
   <si>
-    <t>Không nhập ngày khám nhưng hệ thống không cảnh báo lỗi.</t>
-  </si>
-  <si>
     <t>TC_31</t>
   </si>
   <si>
@@ -987,9 +860,6 @@
     <t>Hiển thị thông báo lỗi "Vui lòng nhập thông tin lịch hẹn"</t>
   </si>
   <si>
-    <t>Không nhập bất kỳ thông tin nào nhưng vẫn có thể gửi form đặt lịch.</t>
-  </si>
-  <si>
     <t>TC_32</t>
   </si>
   <si>
@@ -1008,9 +878,6 @@
     <t>Hiển thị đầy đủ, không lag</t>
   </si>
   <si>
-    <t>Lịch sử lịch hẹn hiển thị thiếu hoặc sai dữ liệu.</t>
-  </si>
-  <si>
     <t>TC_33</t>
   </si>
   <si>
@@ -1029,9 +896,6 @@
     <t>Chỉ hiển thị lịch trong ngày đã chọn</t>
   </si>
   <si>
-    <t>Lọc lịch hẹn theo ngày trả về kết quả không chính xác.</t>
-  </si>
-  <si>
     <t>TC_34</t>
   </si>
   <si>
@@ -1050,9 +914,6 @@
     <t>Hiển thị lịch trong tuần được chọn</t>
   </si>
   <si>
-    <t>Lọc lịch hẹn theo tuần hiển thị sai phạm vi ngày.</t>
-  </si>
-  <si>
     <t>TC_35</t>
   </si>
   <si>
@@ -1071,9 +932,6 @@
     <t>Hiển thị lịch trong tháng 12</t>
   </si>
   <si>
-    <t>Lọc lịch hẹn theo tháng không bao gồm đầy đủ các lịch trong tháng.</t>
-  </si>
-  <si>
     <t>TC_36</t>
   </si>
   <si>
@@ -1098,9 +956,6 @@
     <t>Trạng thái lịch chuyển sang “Đã hủy”</t>
   </si>
   <si>
-    <t>Sau khi huỷ lịch hẹn thành công, trạng thái không được cập nhật ngay.</t>
-  </si>
-  <si>
     <t>TC_37</t>
   </si>
   <si>
@@ -1122,9 +977,6 @@
     <t>Tạo lịch hẹn thành công</t>
   </si>
   <si>
-    <t>Thêm lịch hẹn thành công nhưng không hiển thị trên danh sách.</t>
-  </si>
-  <si>
     <t>TC_38</t>
   </si>
   <si>
@@ -1140,9 +992,6 @@
     <t>Hiển thị lỗi "Thêm không hợp lệ"</t>
   </si>
   <si>
-    <t>Không nhập khoa nhưng hệ thống chỉ báo lỗi chung chung, không rõ ràng.</t>
-  </si>
-  <si>
     <t>TC_39</t>
   </si>
   <si>
@@ -1155,9 +1004,6 @@
     <t>Hiển thị lỗi "Ngày không hợp lệ"</t>
   </si>
   <si>
-    <t>Không nhập ngày nhưng thông báo lỗi không đúng vị trí.</t>
-  </si>
-  <si>
     <t>TC_40</t>
   </si>
   <si>
@@ -1176,9 +1022,6 @@
     <t>Hiển thị lịch thuộc khoa Nhi</t>
   </si>
   <si>
-    <t>Tìm kiếm lịch hẹn theo khoa trả về dữ liệu không liên quan.</t>
-  </si>
-  <si>
     <t>TC_41</t>
   </si>
   <si>
@@ -1197,9 +1040,6 @@
     <t>Hiển thị lịch của bác sĩ Trần B</t>
   </si>
   <si>
-    <t>Tìm kiếm theo bác sĩ không phân biệt chính xác bác sĩ trùng tên.</t>
-  </si>
-  <si>
     <t>TC_42</t>
   </si>
   <si>
@@ -1218,9 +1058,6 @@
     <t>Trạng thái chuyển sang “Đã tiếp nhận"</t>
   </si>
   <si>
-    <t>Hệ thống cho phép tiếp nhận bệnh nhân trước thời gian lịch hẹn.</t>
-  </si>
-  <si>
     <t>TC_43</t>
   </si>
   <si>
@@ -1236,9 +1073,6 @@
     <t>Hiển thị lỗi, không cho tiếp nhận</t>
   </si>
   <si>
-    <t>Vẫn cho phép tiếp nhận bệnh nhân với lịch hẹn đã bị huỷ.</t>
-  </si>
-  <si>
     <t>TC_44</t>
   </si>
   <si>
@@ -1257,9 +1091,6 @@
     <t>Hiển thị đúng lịch hẹn</t>
   </si>
   <si>
-    <t>Tìm kiếm theo mã lịch hẹn không trả về kết quả dù mã tồn tại.</t>
-  </si>
-  <si>
     <t>TC_45</t>
   </si>
   <si>
@@ -1275,9 +1106,6 @@
     <t>Hiển thị lịch của bệnh nhân</t>
   </si>
   <si>
-    <t>Tìm kiếm theo số điện thoại trả về sai bệnh nhân.</t>
-  </si>
-  <si>
     <t>TC_46</t>
   </si>
   <si>
@@ -1293,9 +1121,6 @@
     <t>Hiển thị đúng bệnh nhân</t>
   </si>
   <si>
-    <t>Tìm kiếm theo CCCD không hoạt động đúng.</t>
-  </si>
-  <si>
     <t>TC_47</t>
   </si>
   <si>
@@ -1317,9 +1142,6 @@
     <t>Hiển thị bệnh nhân trong ngày</t>
   </si>
   <si>
-    <t>Danh sách bệnh nhân trong ngày hiển thị thiếu dữ liệu.</t>
-  </si>
-  <si>
     <t>TC_48</t>
   </si>
   <si>
@@ -1335,9 +1157,6 @@
     <t>Hiển thị danh sách bệnh nhân đúng ngày</t>
   </si>
   <si>
-    <t>Xem danh sách bệnh nhân theo ngày nhưng dữ liệu không đồng bộ.</t>
-  </si>
-  <si>
     <t>TC_49</t>
   </si>
   <si>
@@ -1356,9 +1175,6 @@
     <t>Hiển thi đúng dữ liệu trang 2</t>
   </si>
   <si>
-    <t>Phân trang danh sách bệnh nhân không hoạt động đúng.</t>
-  </si>
-  <si>
     <t>TC_50</t>
   </si>
   <si>
@@ -1374,9 +1190,6 @@
     <t>Hệ thống chuyển về màn hình đăng nhập</t>
   </si>
   <si>
-    <t>Người dùng chưa đăng nhập vẫn truy cập được màn hình hẹn.</t>
-  </si>
-  <si>
     <t>TC_51</t>
   </si>
   <si>
@@ -1392,9 +1205,6 @@
     <t>2. Chọn ngày quá khứ</t>
   </si>
   <si>
-    <t>Hệ thống cho phép đặt lịch hẹn với ngày trong quá khứ.</t>
-  </si>
-  <si>
     <t>TC_52</t>
   </si>
   <si>
@@ -1410,9 +1220,6 @@
     <t>Hiển thị lỗi "Bác sĩ đã có lịch"</t>
   </si>
   <si>
-    <t>Hệ thống không kiểm tra trùng giờ khám của bác sĩ.</t>
-  </si>
-  <si>
     <t>12/20/2025 9:00</t>
   </si>
   <si>
@@ -1434,9 +1241,6 @@
     <t>Hiển thị trang trống hoặc tự quay về trang cuối</t>
   </si>
   <si>
-    <t>Truy cập trang vượt quá số trang nhưng không có thông báo lỗi.</t>
-  </si>
-  <si>
     <t>TC_54</t>
   </si>
   <si>
@@ -1447,9 +1251,6 @@
   </si>
   <si>
     <t>Truy cập màn hình lịch</t>
-  </si>
-  <si>
-    <t>Khi API tải lịch trả lỗi, hệ thống không xử lý và không hiển thị thông báo.</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1263,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1473,12 +1274,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -1625,12 +1420,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1833,7 +1622,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1860,19 +1649,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1890,30 +1666,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -2037,137 +1789,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2183,35 +1935,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2746,8 +2477,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H150"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G150"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818" customWidth="1"/>
     <col min="2" max="2" width="24.3636363636364" customWidth="1"/>
@@ -2758,7 +2489,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2780,547 +2511,492 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="42" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" ht="28" spans="1:8">
+    </row>
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:8">
+    </row>
+    <row r="4" customHeight="1" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
       <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="2"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="2"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
       <c r="D8" s="2"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
       <c r="D9" s="2"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" ht="28" spans="1:8">
+    </row>
+    <row r="11" ht="28" spans="1:7">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:8">
+    </row>
+    <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:8">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:8">
-      <c r="A15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:8">
+      <c r="G15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:8">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:7">
       <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="F19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="F20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="F21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" spans="1:7">
+      <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="1:8">
-      <c r="A24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" ht="28" spans="1:8">
+    </row>
+    <row r="25" ht="28" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="26" customHeight="1" spans="1:7">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>63</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
       <c r="F27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8">
+        <v>64</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="2"/>
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" ht="28" spans="1:8">
+    </row>
+    <row r="30" ht="28" spans="1:7">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8">
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:8">
+        <v>70</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8">
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8">
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:8">
+        <v>76</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:8">
+    </row>
+    <row r="36" customHeight="1" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3328,9 +3004,8 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8">
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3338,47 +3013,42 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8">
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:8">
+        <v>83</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8">
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3386,1027 +3056,924 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8">
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>89</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>95</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8">
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>32</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E46" s="13">
+        <v>103</v>
+      </c>
+      <c r="E46" s="7">
         <v>45916</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>105</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8">
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="E52" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="G52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="D53" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" ht="18" customHeight="1" spans="1:8">
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>134</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>139</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>143</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8">
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>147</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8">
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" ht="42" customHeight="1" spans="1:8">
+        <v>151</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1" spans="1:7">
       <c r="A61" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8">
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8">
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="2" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:8">
+        <v>158</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:7">
       <c r="A64" s="1" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" ht="42" customHeight="1" spans="1:8">
+    </row>
+    <row r="65" ht="42" customHeight="1" spans="1:7">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8">
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>166</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="1"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:8">
+    </row>
+    <row r="68" customHeight="1" spans="1:7">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8">
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8">
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:8">
+    </row>
+    <row r="71" customHeight="1" spans="1:7">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:8">
+    </row>
+    <row r="72" customHeight="1" spans="1:7">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="1"/>
-    </row>
-    <row r="74" spans="1:8">
+        <v>177</v>
+      </c>
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="75" spans="1:8">
+        <v>17</v>
+      </c>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="1"/>
-    </row>
-    <row r="76" spans="1:8">
+        <v>178</v>
+      </c>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="1"/>
-    </row>
-    <row r="77" ht="42" customHeight="1" spans="1:8">
+        <v>179</v>
+      </c>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" ht="42" customHeight="1" spans="1:7">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="1:8">
+        <v>180</v>
+      </c>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="1" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="1"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:8">
+    </row>
+    <row r="79" customHeight="1" spans="1:7">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8">
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:8">
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:8">
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-    </row>
-    <row r="83" ht="42" customHeight="1" spans="1:8">
+    </row>
+    <row r="83" ht="42" customHeight="1" spans="1:7">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>185</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="1" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="1"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:8">
+    </row>
+    <row r="85" customHeight="1" spans="1:7">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="2" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8">
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8">
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8">
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" ht="42" customHeight="1" spans="1:8">
+    </row>
+    <row r="89" ht="42" customHeight="1" spans="1:7">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>190</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" s="1" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="1"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:8">
+    </row>
+    <row r="91" customHeight="1" spans="1:7">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="2" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8">
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8">
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" ht="27.5" customHeight="1" spans="1:8">
+    </row>
+    <row r="94" ht="27.5" customHeight="1" spans="1:7">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:8">
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1" spans="1:8">
+        <v>195</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1" spans="1:7">
       <c r="A96" s="1" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="1"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="97" ht="26" customHeight="1" spans="1:7">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="2" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" ht="29" customHeight="1" spans="1:8">
+    </row>
+    <row r="98" ht="29" customHeight="1" spans="1:7">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" ht="27" customHeight="1" spans="1:8">
+    </row>
+    <row r="99" ht="27" customHeight="1" spans="1:7">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-    </row>
-    <row r="100" ht="29" customHeight="1" spans="1:8">
+    </row>
+    <row r="100" ht="29" customHeight="1" spans="1:7">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" ht="27" customHeight="1" spans="1:8">
+    </row>
+    <row r="101" ht="27" customHeight="1" spans="1:7">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" ht="36" customHeight="1" spans="1:8">
+        <v>200</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1" spans="1:7">
       <c r="A102" s="1" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="1"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-    </row>
-    <row r="103" ht="31" customHeight="1" spans="1:8">
+    </row>
+    <row r="103" ht="31" customHeight="1" spans="1:7">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4414,896 +3981,800 @@
       <c r="E103" s="3"/>
       <c r="F103" s="1"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-    </row>
-    <row r="104" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="104" ht="26" customHeight="1" spans="1:7">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="2" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="1"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-    </row>
-    <row r="105" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="105" ht="26" customHeight="1" spans="1:7">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1" spans="1:8">
+        <v>204</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1" spans="1:7">
       <c r="A106" s="1" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G106" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="H106" s="3"/>
-    </row>
-    <row r="107" ht="29" customHeight="1" spans="1:8">
+        <v>210</v>
+      </c>
+      <c r="G106" s="3"/>
+    </row>
+    <row r="107" ht="29" customHeight="1" spans="1:7">
       <c r="A107" s="1" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E107" s="13">
+        <v>214</v>
+      </c>
+      <c r="E107" s="7">
         <v>46012</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="108" ht="26" customHeight="1" spans="1:7">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="2" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" ht="29" customHeight="1" spans="1:8">
+        <v>216</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" ht="29" customHeight="1" spans="1:7">
       <c r="A109" s="1" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" ht="25" customHeight="1" spans="1:8">
+        <v>222</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" ht="25" customHeight="1" spans="1:7">
       <c r="A110" s="1" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" ht="27" customHeight="1" spans="1:8">
+        <v>228</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" ht="27" customHeight="1" spans="1:7">
       <c r="A111" s="1" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="1"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-    </row>
-    <row r="112" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="112" ht="26" customHeight="1" spans="1:7">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="2" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" ht="33" customHeight="1" spans="1:8">
+    </row>
+    <row r="113" ht="33" customHeight="1" spans="1:7">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="2" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" ht="26" customHeight="1" spans="1:8">
+        <v>236</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1" spans="1:7">
       <c r="A114" s="1" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-    </row>
-    <row r="115" ht="30" customHeight="1" spans="1:8">
+    </row>
+    <row r="115" ht="30" customHeight="1" spans="1:7">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="2" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-    </row>
-    <row r="116" ht="25" customHeight="1" spans="1:8">
+    </row>
+    <row r="116" ht="25" customHeight="1" spans="1:7">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" ht="29" customHeight="1" spans="1:8">
+        <v>243</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" ht="29" customHeight="1" spans="1:7">
       <c r="A117" s="1" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" ht="35" customHeight="1" spans="1:8">
+    </row>
+    <row r="118" ht="35" customHeight="1" spans="1:7">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="2" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" ht="29" customHeight="1" spans="1:8">
+    </row>
+    <row r="119" ht="29" customHeight="1" spans="1:7">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="120" ht="29" customHeight="1" spans="1:8">
+        <v>248</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" ht="29" customHeight="1" spans="1:7">
       <c r="A120" s="1" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-    </row>
-    <row r="121" ht="25" customHeight="1" spans="1:8">
+    </row>
+    <row r="121" ht="25" customHeight="1" spans="1:7">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="2" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-    </row>
-    <row r="122" ht="30" customHeight="1" spans="1:8">
+    </row>
+    <row r="122" ht="30" customHeight="1" spans="1:7">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" ht="26" customHeight="1" spans="1:8">
+        <v>252</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1" spans="1:7">
       <c r="A123" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-    </row>
-    <row r="124" ht="31" customHeight="1" spans="1:8">
+    </row>
+    <row r="124" ht="31" customHeight="1" spans="1:7">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="125" ht="32" customHeight="1" spans="1:8">
+        <v>258</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" ht="32" customHeight="1" spans="1:7">
       <c r="A125" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
-    </row>
-    <row r="126" ht="28" customHeight="1" spans="1:8">
+    </row>
+    <row r="126" ht="28" customHeight="1" spans="1:7">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="127" ht="37" customHeight="1" spans="1:8">
+        <v>264</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" ht="37" customHeight="1" spans="1:7">
       <c r="A127" s="1" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
-    </row>
-    <row r="128" ht="41" customHeight="1" spans="1:8">
+    </row>
+    <row r="128" ht="41" customHeight="1" spans="1:7">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="2" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="129" ht="42" customHeight="1" spans="1:8">
+        <v>270</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1" spans="1:7">
       <c r="A129" s="1" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-    </row>
-    <row r="130" spans="1:8">
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="2" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+        <v>275</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" s="1" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-    </row>
-    <row r="132" spans="1:8">
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="133" ht="31" customHeight="1" spans="1:8">
+        <v>281</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" ht="31" customHeight="1" spans="1:7">
       <c r="A133" s="1" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1">
         <v>912345678</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-    </row>
-    <row r="134" ht="27" customHeight="1" spans="1:8">
+    </row>
+    <row r="134" ht="27" customHeight="1" spans="1:7">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="135" ht="29" customHeight="1" spans="1:8">
+        <v>286</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" ht="29" customHeight="1" spans="1:7">
       <c r="A135" s="1" t="s">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1">
         <v>79123456789</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-    </row>
-    <row r="136" ht="26" customHeight="1" spans="1:8">
+    </row>
+    <row r="136" ht="26" customHeight="1" spans="1:7">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G136" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="H136" s="3"/>
-    </row>
-    <row r="137" ht="24" customHeight="1" spans="1:8">
+        <v>291</v>
+      </c>
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137" ht="24" customHeight="1" spans="1:7">
       <c r="A137" s="1" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
-    </row>
-    <row r="138" ht="24" customHeight="1" spans="1:8">
+    </row>
+    <row r="138" ht="24" customHeight="1" spans="1:7">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="2" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
-    </row>
-    <row r="139" ht="28" customHeight="1" spans="1:8">
+    </row>
+    <row r="139" ht="28" customHeight="1" spans="1:7">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="2" t="s">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-    </row>
-    <row r="140" ht="25" customHeight="1" spans="1:8">
+    </row>
+    <row r="140" ht="25" customHeight="1" spans="1:7">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="141" ht="26" customHeight="1" spans="1:8">
+        <v>298</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" ht="26" customHeight="1" spans="1:7">
       <c r="A141" s="1" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E141" s="13">
+        <v>302</v>
+      </c>
+      <c r="E141" s="7">
         <v>46015</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="142" ht="25" customHeight="1" spans="1:8">
+        <v>303</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" ht="25" customHeight="1" spans="1:7">
       <c r="A142" s="1" t="s">
-        <v>353</v>
+        <v>304</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
+        <v>309</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" s="1" t="s">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>361</v>
+        <v>311</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>362</v>
+        <v>312</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>363</v>
+        <v>313</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+        <v>314</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" s="1" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
-    </row>
-    <row r="145" spans="1:8">
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E145" s="13">
+        <v>319</v>
+      </c>
+      <c r="E145" s="7">
         <v>42109</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
-    </row>
-    <row r="146" spans="1:8">
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
       <c r="D146" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="1:8">
+        <v>252</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:7">
       <c r="A147" s="1" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>324</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="2" t="s">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="F148" s="1"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="1"/>
-    </row>
-    <row r="149" spans="1:8">
+      <c r="G148" s="1"/>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" s="1" t="s">
-        <v>379</v>
+        <v>326</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>383</v>
+        <v>330</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+        <v>331</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" s="1" t="s">
-        <v>386</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>387</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>388</v>
+        <v>334</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="118">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A10:A11"/>
@@ -5403,29 +4874,25 @@
     <mergeCell ref="F102:F103"/>
     <mergeCell ref="F137:F139"/>
     <mergeCell ref="F147:F148"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G18:G22"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="G68:G71"/>
     <mergeCell ref="G72:G77"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="H18:H22"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="H68:H71"/>
-    <mergeCell ref="H72:H77"/>
-    <mergeCell ref="H79:H82"/>
-    <mergeCell ref="H85:H88"/>
-    <mergeCell ref="H91:H94"/>
-    <mergeCell ref="H97:H100"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="H137:H139"/>
-    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="G85:G88"/>
+    <mergeCell ref="G91:G94"/>
+    <mergeCell ref="G97:G100"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G137:G139"/>
+    <mergeCell ref="G147:G148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
